--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92675</v>
+        <v>92678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92678</v>
+        <v>92679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92688</v>
+        <v>92690</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92690</v>
+        <v>92691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92691</v>
+        <v>92697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37645-2026 artfynd.xlsx
+++ b/artfynd/A 37645-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481035</v>
       </c>
       <c r="B2" t="n">
-        <v>92697</v>
+        <v>92701</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
